--- a/ebd/static/lista de revistas.xlsx
+++ b/ebd/static/lista de revistas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PDV-01\Desktop\aula2\ebd\static\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FE796A8-9B2F-4E6B-9258-7AC18007AE3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9696D981-FFFE-48CF-B8D7-1F4252684A71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{2B98A784-99CC-4906-9103-6760237A2AE9}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="77">
   <si>
     <t>id</t>
   </si>
@@ -248,6 +248,15 @@
   </si>
   <si>
     <t>/static/imagem28.png</t>
+  </si>
+  <si>
+    <t>Devorcinal A Santissima Trindade</t>
+  </si>
+  <si>
+    <t>Devorcinal</t>
+  </si>
+  <si>
+    <t>/static/imagem29.png</t>
   </si>
 </sst>
 </file>
@@ -1230,6 +1239,26 @@
         <v>72</v>
       </c>
     </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>991001</v>
+      </c>
+      <c r="B30">
+        <v>0</v>
+      </c>
+      <c r="C30" t="s">
+        <v>74</v>
+      </c>
+      <c r="D30" t="s">
+        <v>75</v>
+      </c>
+      <c r="E30" s="5">
+        <v>15</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C32" s="1"/>
     </row>

--- a/ebd/static/lista de revistas.xlsx
+++ b/ebd/static/lista de revistas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PDV-01\Desktop\aula2\ebd\static\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9696D981-FFFE-48CF-B8D7-1F4252684A71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DEB6D67-6338-420C-BF16-10236AF8719D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{2B98A784-99CC-4906-9103-6760237A2AE9}"/>
   </bookViews>
@@ -250,13 +250,13 @@
     <t>/static/imagem28.png</t>
   </si>
   <si>
-    <t>Devorcinal A Santissima Trindade</t>
-  </si>
-  <si>
     <t>Devorcinal</t>
   </si>
   <si>
     <t>/static/imagem29.png</t>
+  </si>
+  <si>
+    <t>Devocinal A Santissima Trindade</t>
   </si>
 </sst>
 </file>
@@ -1247,16 +1247,16 @@
         <v>0</v>
       </c>
       <c r="C30" t="s">
+        <v>76</v>
+      </c>
+      <c r="D30" t="s">
         <v>74</v>
-      </c>
-      <c r="D30" t="s">
-        <v>75</v>
       </c>
       <c r="E30" s="5">
         <v>15</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">

--- a/ebd/static/lista de revistas.xlsx
+++ b/ebd/static/lista de revistas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PDV-01\Desktop\aula2\ebd\static\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DEB6D67-6338-420C-BF16-10236AF8719D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77CB0E0D-0DA9-4684-BD8D-5E648C82FBBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{2B98A784-99CC-4906-9103-6760237A2AE9}"/>
   </bookViews>
@@ -263,7 +263,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -298,6 +301,32 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -307,7 +336,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -315,11 +344,77 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -332,9 +427,27 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{A5FC7A7A-2BBE-4114-A660-440305D94F41}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -649,11 +762,11 @@
   <dimension ref="A1:J32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" style="5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="65.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -678,8 +791,8 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>9500</v>
+      <c r="A2" s="6">
+        <v>950001</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -690,16 +803,16 @@
       <c r="D2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="5">
-        <v>10</v>
+      <c r="E2" s="9">
+        <v>11.3</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>9550</v>
+      <c r="A3" s="6">
+        <v>955001</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -710,8 +823,8 @@
       <c r="D3" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="5">
-        <v>15</v>
+      <c r="E3" s="10">
+        <v>17</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>10</v>
@@ -719,8 +832,8 @@
       <c r="I3" s="3"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>140554</v>
+      <c r="A4" s="6">
+        <v>14055401</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -731,16 +844,16 @@
       <c r="D4" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="5">
-        <v>17</v>
+      <c r="E4" s="10">
+        <v>19.3</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>140573</v>
+      <c r="A5" s="6">
+        <v>14057301</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -751,16 +864,16 @@
       <c r="D5" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="5">
-        <v>19</v>
+      <c r="E5" s="10">
+        <v>22</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>180744</v>
+      <c r="A6" s="6">
+        <v>19074401</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -771,16 +884,16 @@
       <c r="D6" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="5">
-        <v>30</v>
+      <c r="E6" s="10">
+        <v>33</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>9400</v>
+      <c r="A7" s="7">
+        <v>940001</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -791,16 +904,16 @@
       <c r="D7" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="5">
-        <v>10</v>
+      <c r="E7" s="10">
+        <v>11.3</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>9450</v>
+      <c r="A8" s="7">
+        <v>945001</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -811,16 +924,16 @@
       <c r="D8" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="5">
-        <v>15</v>
+      <c r="E8" s="10">
+        <v>17</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>9200</v>
+      <c r="A9" s="7">
+        <v>920001</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -831,16 +944,16 @@
       <c r="D9" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="5">
-        <v>10</v>
+      <c r="E9" s="10">
+        <v>11.3</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>9250</v>
+      <c r="A10" s="7">
+        <v>925001</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -851,16 +964,16 @@
       <c r="D10" t="s">
         <v>22</v>
       </c>
-      <c r="E10" s="5">
-        <v>15</v>
+      <c r="E10" s="10">
+        <v>17</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>133733</v>
+      <c r="A11" s="7">
+        <v>13373301</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -871,16 +984,16 @@
       <c r="D11" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="5">
-        <v>10</v>
+      <c r="E11" s="10">
+        <v>11.3</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>133753</v>
+      <c r="A12" s="7">
+        <v>13375301</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -891,16 +1004,16 @@
       <c r="D12" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="5">
-        <v>15</v>
+      <c r="E12" s="11">
+        <v>17</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>9100</v>
+      <c r="A13" s="7">
+        <v>910001</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -911,16 +1024,16 @@
       <c r="D13" t="s">
         <v>28</v>
       </c>
-      <c r="E13" s="5">
-        <v>8</v>
+      <c r="E13" s="12">
+        <v>9</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>9150</v>
+      <c r="A14" s="7">
+        <v>915001</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -931,8 +1044,8 @@
       <c r="D14" t="s">
         <v>28</v>
       </c>
-      <c r="E14" s="5">
-        <v>13</v>
+      <c r="E14" s="13">
+        <v>14.5</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>57</v>
@@ -940,8 +1053,8 @@
       <c r="J14" s="1"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>122234</v>
+      <c r="A15" s="7">
+        <v>12223401</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -952,16 +1065,16 @@
       <c r="D15" t="s">
         <v>28</v>
       </c>
-      <c r="E15" s="5">
-        <v>35</v>
+      <c r="E15" s="14">
+        <v>38</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>9000</v>
+      <c r="A16" s="7">
+        <v>900001</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -972,16 +1085,16 @@
       <c r="D16" t="s">
         <v>32</v>
       </c>
-      <c r="E16" s="5">
-        <v>8</v>
+      <c r="E16" s="12">
+        <v>9</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>9050</v>
+      <c r="A17" s="7">
+        <v>905001</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -992,16 +1105,16 @@
       <c r="D17" t="s">
         <v>32</v>
       </c>
-      <c r="E17" s="5">
-        <v>13</v>
+      <c r="E17" s="13">
+        <v>14.5</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>122233</v>
+      <c r="A18" s="7">
+        <v>12223301</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1012,16 +1125,16 @@
       <c r="D18" t="s">
         <v>35</v>
       </c>
-      <c r="E18" s="5">
-        <v>35</v>
+      <c r="E18" s="14">
+        <v>38</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>9300</v>
+      <c r="A19" s="7">
+        <v>930001</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1032,16 +1145,16 @@
       <c r="D19" t="s">
         <v>37</v>
       </c>
-      <c r="E19" s="5">
-        <v>8</v>
+      <c r="E19" s="12">
+        <v>9</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>9350</v>
+      <c r="A20" s="7">
+        <v>935001</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1052,16 +1165,16 @@
       <c r="D20" t="s">
         <v>37</v>
       </c>
-      <c r="E20" s="5">
-        <v>13</v>
+      <c r="E20" s="13">
+        <v>14.5</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>122228</v>
+      <c r="A21" s="7">
+        <v>12222801</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1072,16 +1185,16 @@
       <c r="D21" t="s">
         <v>37</v>
       </c>
-      <c r="E21" s="5">
-        <v>35</v>
+      <c r="E21" s="14">
+        <v>38</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>9700</v>
+      <c r="A22" s="7">
+        <v>970001</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -1092,16 +1205,16 @@
       <c r="D22" t="s">
         <v>41</v>
       </c>
-      <c r="E22" s="5">
-        <v>8</v>
+      <c r="E22" s="12">
+        <v>9</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>9750</v>
+      <c r="A23" s="7">
+        <v>975001</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -1112,16 +1225,16 @@
       <c r="D23" t="s">
         <v>41</v>
       </c>
-      <c r="E23" s="5">
-        <v>13</v>
+      <c r="E23" s="13">
+        <v>14.5</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>122227</v>
+      <c r="A24" s="7">
+        <v>12222701</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -1132,16 +1245,16 @@
       <c r="D24" t="s">
         <v>41</v>
       </c>
-      <c r="E24" s="5">
-        <v>35</v>
+      <c r="E24" s="14">
+        <v>38</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>133713</v>
+      <c r="A25" s="7">
+        <v>13371301</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -1152,16 +1265,16 @@
       <c r="D25" t="s">
         <v>45</v>
       </c>
-      <c r="E25" s="5">
-        <v>13</v>
+      <c r="E25" s="15">
+        <v>14</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>122235</v>
+      <c r="A26" s="7">
+        <v>12223501</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -1172,16 +1285,16 @@
       <c r="D26" t="s">
         <v>45</v>
       </c>
-      <c r="E26" s="5">
-        <v>25</v>
+      <c r="E26" s="15">
+        <v>28</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>6400</v>
+      <c r="A27" s="7">
+        <v>640001</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -1192,16 +1305,16 @@
       <c r="D27" t="s">
         <v>48</v>
       </c>
-      <c r="E27" s="5">
-        <v>14</v>
+      <c r="E27" s="12">
+        <v>17</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>9950</v>
+      <c r="A28" s="7">
+        <v>995001</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -1212,16 +1325,16 @@
       <c r="D28" t="s">
         <v>48</v>
       </c>
-      <c r="E28" s="5">
-        <v>14</v>
+      <c r="E28" s="13">
+        <v>20</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>99999</v>
+      <c r="A29" s="8">
+        <v>991001</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -1232,16 +1345,16 @@
       <c r="D29" t="s">
         <v>51</v>
       </c>
-      <c r="E29" s="5">
-        <v>20</v>
+      <c r="E29" s="14">
+        <v>15</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>991001</v>
+    <row r="30" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="6">
+        <v>376066</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -1252,8 +1365,8 @@
       <c r="D30" t="s">
         <v>74</v>
       </c>
-      <c r="E30" s="5">
-        <v>15</v>
+      <c r="E30" s="16">
+        <v>20</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>75</v>

--- a/ebd/static/lista de revistas.xlsx
+++ b/ebd/static/lista de revistas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PDV-01\Desktop\aula2\ebd\static\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77CB0E0D-0DA9-4684-BD8D-5E648C82FBBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41C96AB1-A9C0-4AA3-8261-07586274FF67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{2B98A784-99CC-4906-9103-6760237A2AE9}"/>
   </bookViews>
@@ -1346,7 +1346,7 @@
         <v>51</v>
       </c>
       <c r="E29" s="14">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>72</v>
@@ -1366,7 +1366,7 @@
         <v>74</v>
       </c>
       <c r="E30" s="16">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>75</v>

--- a/ebd/static/lista de revistas.xlsx
+++ b/ebd/static/lista de revistas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PDV-01\Desktop\aula2\ebd\static\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41C96AB1-A9C0-4AA3-8261-07586274FF67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89535327-5110-42EA-9DB2-030954E72CC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{2B98A784-99CC-4906-9103-6760237A2AE9}"/>
   </bookViews>
@@ -266,7 +266,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -327,16 +327,140 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFCC0000"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF808080"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF006600"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF0000EE"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF996600"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF000000"/>
+        <bgColor rgb="FF111111"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF808080"/>
+        <bgColor rgb="FF969696"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDDDDD"/>
+        <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCCCC"/>
+        <bgColor rgb="FFDDDDDD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC0000"/>
+        <bgColor rgb="FF800000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCFFCC"/>
+        <bgColor rgb="FFCCFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -409,12 +533,60 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF808080"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="6" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="6" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -444,10 +616,46 @@
     <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="4" fontId="9" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="21" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="35">
+    <cellStyle name="Accent 1 14" xfId="3" xr:uid="{793F2E1C-90B9-4301-82D5-E7D4A66F7262}"/>
+    <cellStyle name="Accent 1 15" xfId="4" xr:uid="{C3135ADC-4EE6-4ADF-A34D-A171CB7DECEA}"/>
+    <cellStyle name="Accent 13" xfId="5" xr:uid="{3A728A45-9090-4A4C-90FC-652A737CAF0F}"/>
+    <cellStyle name="Accent 14" xfId="6" xr:uid="{9996BEE8-0903-4CA3-927D-AFCF1BAC328D}"/>
+    <cellStyle name="Accent 2 15" xfId="7" xr:uid="{2FAD4B55-B65F-4F66-8877-E59CF39BEE21}"/>
+    <cellStyle name="Accent 2 16" xfId="8" xr:uid="{5B129720-A8BC-44F1-9C4E-5B2AF0C9DD47}"/>
+    <cellStyle name="Accent 3 16" xfId="9" xr:uid="{E46D6A1C-AF30-49F4-B619-64AC29CECBA0}"/>
+    <cellStyle name="Accent 3 17" xfId="10" xr:uid="{92AD8362-A42C-4436-A4E2-39A53A700086}"/>
+    <cellStyle name="Bad 10" xfId="11" xr:uid="{C7931A9A-BD3A-4E12-A397-70E409938671}"/>
+    <cellStyle name="Bad 11" xfId="12" xr:uid="{18479FBA-0399-4D26-9631-C5EDDF711110}"/>
+    <cellStyle name="Error 12" xfId="13" xr:uid="{C27BDCA4-BBE5-425C-8BD8-CE15515EBB23}"/>
+    <cellStyle name="Error 13" xfId="14" xr:uid="{812B0E01-928D-4D52-8CA0-8B8E6E6EDC48}"/>
+    <cellStyle name="Footnote 5" xfId="15" xr:uid="{76E0247D-789E-4500-A451-10AAA387DBD3}"/>
+    <cellStyle name="Footnote 6" xfId="16" xr:uid="{BD9BBBFE-244E-487A-B96F-510841FE89DF}"/>
+    <cellStyle name="Good 8" xfId="17" xr:uid="{416F59B5-867A-482D-80DA-6AB7088D7CFA}"/>
+    <cellStyle name="Good 9" xfId="18" xr:uid="{C79A0294-8792-4DD2-A9A2-9960FDD99F8D}"/>
+    <cellStyle name="Heading 1 1" xfId="19" xr:uid="{6C807100-C71E-43F4-9ED0-AA04847A9AEB}"/>
+    <cellStyle name="Heading 1 2" xfId="20" xr:uid="{56AB1F6F-11C4-47B4-9C73-E39879C9CD61}"/>
+    <cellStyle name="Heading 2 2" xfId="21" xr:uid="{242D8976-7E61-4EDF-9D7F-53A78DFF29F4}"/>
+    <cellStyle name="Heading 2 3" xfId="22" xr:uid="{65844357-04E5-4C36-8C28-4A5B982D52E0}"/>
+    <cellStyle name="Hyperlink 6" xfId="23" xr:uid="{074F5B94-B50E-4103-9D58-F88A52A3B118}"/>
+    <cellStyle name="Hyperlink 7" xfId="24" xr:uid="{A6FDDD1D-5F9F-4663-93B2-92AB0B5334E8}"/>
+    <cellStyle name="Neutral 10" xfId="25" xr:uid="{9BDC26BB-53AD-41CE-B3E3-4F28B3B5A8EA}"/>
+    <cellStyle name="Neutral 9" xfId="26" xr:uid="{A667141E-6AFD-47BC-87D1-130A18BDF70C}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{A5FC7A7A-2BBE-4114-A660-440305D94F41}"/>
+    <cellStyle name="Normal 3" xfId="2" xr:uid="{9EC4EEF4-027D-4D22-962A-7E4F5437BCB9}"/>
+    <cellStyle name="Note 4" xfId="27" xr:uid="{9DAB07DE-3D3E-4983-A082-E7B9225F4245}"/>
+    <cellStyle name="Note 5" xfId="28" xr:uid="{CECA1D58-2C0D-43FB-9ED1-4C8B1BDB5320}"/>
+    <cellStyle name="Status 7" xfId="29" xr:uid="{3DD9194A-0CB5-4EDC-A895-EF3AC26598B9}"/>
+    <cellStyle name="Status 8" xfId="30" xr:uid="{6E26ECF8-89F1-4A16-B1B4-D39E30D23AE8}"/>
+    <cellStyle name="Text 3" xfId="31" xr:uid="{B1158CA1-2E79-454B-AD87-5B91F64E8554}"/>
+    <cellStyle name="Text 4" xfId="32" xr:uid="{C08C9B71-B202-479E-B416-631E9D2E4FA3}"/>
+    <cellStyle name="Warning 11" xfId="33" xr:uid="{C96C8233-D80C-499F-A45F-90102C911A08}"/>
+    <cellStyle name="Warning 12" xfId="34" xr:uid="{3A6AE4AC-BC13-4A80-B437-09F5CD886715}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -759,7 +967,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4983B69-2705-409E-BD05-347C2EC497A2}">
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -804,11 +1012,12 @@
         <v>7</v>
       </c>
       <c r="E2" s="9">
-        <v>11.3</v>
+        <v>10</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>8</v>
       </c>
+      <c r="H2" s="18"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
@@ -824,11 +1033,12 @@
         <v>7</v>
       </c>
       <c r="E3" s="10">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="H3" s="18"/>
       <c r="I3" s="3"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -845,11 +1055,12 @@
         <v>7</v>
       </c>
       <c r="E4" s="10">
-        <v>19.3</v>
+        <v>19</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>73</v>
       </c>
+      <c r="H4" s="17"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
@@ -865,11 +1076,12 @@
         <v>7</v>
       </c>
       <c r="E5" s="10">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="H5" s="18"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
@@ -885,11 +1097,12 @@
         <v>7</v>
       </c>
       <c r="E6" s="10">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>15</v>
       </c>
+      <c r="H6" s="19"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
@@ -905,11 +1118,12 @@
         <v>17</v>
       </c>
       <c r="E7" s="10">
-        <v>11.3</v>
+        <v>10</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>18</v>
       </c>
+      <c r="H7" s="18"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
@@ -925,11 +1139,12 @@
         <v>17</v>
       </c>
       <c r="E8" s="10">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>20</v>
       </c>
+      <c r="H8" s="18"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
@@ -945,11 +1160,12 @@
         <v>22</v>
       </c>
       <c r="E9" s="10">
-        <v>11.3</v>
+        <v>10</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>52</v>
       </c>
+      <c r="H9" s="17"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
@@ -965,11 +1181,12 @@
         <v>22</v>
       </c>
       <c r="E10" s="10">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>53</v>
       </c>
+      <c r="H10" s="17"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
@@ -985,11 +1202,12 @@
         <v>25</v>
       </c>
       <c r="E11" s="10">
-        <v>11.3</v>
+        <v>10</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>54</v>
       </c>
+      <c r="H11" s="17"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="7">
@@ -1005,11 +1223,12 @@
         <v>25</v>
       </c>
       <c r="E12" s="11">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>55</v>
       </c>
+      <c r="H12" s="17"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="7">
@@ -1025,11 +1244,12 @@
         <v>28</v>
       </c>
       <c r="E13" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>56</v>
       </c>
+      <c r="H13" s="17"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="7">
@@ -1045,11 +1265,12 @@
         <v>28</v>
       </c>
       <c r="E14" s="13">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>57</v>
       </c>
+      <c r="H14" s="18"/>
       <c r="J14" s="1"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -1066,11 +1287,12 @@
         <v>28</v>
       </c>
       <c r="E15" s="14">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="H15" s="18"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="7">
@@ -1086,13 +1308,14 @@
         <v>32</v>
       </c>
       <c r="E16" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H16" s="17"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="7">
         <v>905001</v>
       </c>
@@ -1106,13 +1329,14 @@
         <v>32</v>
       </c>
       <c r="E17" s="13">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H17" s="18"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="7">
         <v>12223301</v>
       </c>
@@ -1126,13 +1350,14 @@
         <v>35</v>
       </c>
       <c r="E18" s="14">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H18" s="18"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="7">
         <v>930001</v>
       </c>
@@ -1146,13 +1371,14 @@
         <v>37</v>
       </c>
       <c r="E19" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H19" s="17"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="7">
         <v>935001</v>
       </c>
@@ -1166,13 +1392,14 @@
         <v>37</v>
       </c>
       <c r="E20" s="13">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H20" s="18"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="7">
         <v>12222801</v>
       </c>
@@ -1186,13 +1413,14 @@
         <v>37</v>
       </c>
       <c r="E21" s="14">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H21" s="18"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="7">
         <v>970001</v>
       </c>
@@ -1206,13 +1434,14 @@
         <v>41</v>
       </c>
       <c r="E22" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H22" s="17"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="7">
         <v>975001</v>
       </c>
@@ -1226,13 +1455,14 @@
         <v>41</v>
       </c>
       <c r="E23" s="13">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H23" s="18"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="7">
         <v>12222701</v>
       </c>
@@ -1246,13 +1476,14 @@
         <v>41</v>
       </c>
       <c r="E24" s="14">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H24" s="18"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="7">
         <v>13371301</v>
       </c>
@@ -1266,13 +1497,14 @@
         <v>45</v>
       </c>
       <c r="E25" s="15">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H25" s="18"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="7">
         <v>12223501</v>
       </c>
@@ -1286,13 +1518,14 @@
         <v>45</v>
       </c>
       <c r="E26" s="15">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H26" s="17"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="7">
         <v>640001</v>
       </c>
@@ -1311,8 +1544,9 @@
       <c r="F27" s="2" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H27" s="18"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="7">
         <v>995001</v>
       </c>
@@ -1331,8 +1565,9 @@
       <c r="F28" s="2" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H28" s="18"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="8">
         <v>991001</v>
       </c>
@@ -1351,8 +1586,9 @@
       <c r="F29" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H29" s="18"/>
+    </row>
+    <row r="30" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6">
         <v>376066</v>
       </c>
@@ -1371,9 +1607,38 @@
       <c r="F30" s="2" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H30" s="17"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H31" s="18"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C32" s="1"/>
+      <c r="H32" s="18"/>
+    </row>
+    <row r="33" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H33" s="18"/>
+    </row>
+    <row r="34" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H34" s="17"/>
+    </row>
+    <row r="35" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H35" s="18"/>
+    </row>
+    <row r="36" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H36" s="18"/>
+    </row>
+    <row r="37" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H37" s="18"/>
+    </row>
+    <row r="38" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H38" s="17"/>
+    </row>
+    <row r="39" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H39" s="18"/>
+    </row>
+    <row r="40" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H40" s="18"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/ebd/static/lista de revistas.xlsx
+++ b/ebd/static/lista de revistas.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PDV-01\Desktop\aula2\ebd\static\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PDV-01\Desktop\Nova pasta (5)\ebdpesqueira\ebd\static\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89535327-5110-42EA-9DB2-030954E72CC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D7E00A7-645B-41BC-BB60-B26F5588C9FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{2B98A784-99CC-4906-9103-6760237A2AE9}"/>
   </bookViews>
@@ -1012,7 +1012,7 @@
         <v>7</v>
       </c>
       <c r="E2" s="9">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>8</v>
@@ -1033,7 +1033,7 @@
         <v>7</v>
       </c>
       <c r="E3" s="10">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>10</v>
@@ -1097,7 +1097,7 @@
         <v>7</v>
       </c>
       <c r="E6" s="10">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>15</v>
@@ -1118,7 +1118,7 @@
         <v>17</v>
       </c>
       <c r="E7" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>18</v>
@@ -1139,7 +1139,7 @@
         <v>17</v>
       </c>
       <c r="E8" s="10">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>20</v>
@@ -1160,7 +1160,7 @@
         <v>22</v>
       </c>
       <c r="E9" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>52</v>
@@ -1181,7 +1181,7 @@
         <v>22</v>
       </c>
       <c r="E10" s="10">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>53</v>
@@ -1202,7 +1202,7 @@
         <v>25</v>
       </c>
       <c r="E11" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>54</v>
@@ -1223,7 +1223,7 @@
         <v>25</v>
       </c>
       <c r="E12" s="11">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>55</v>
@@ -1287,7 +1287,7 @@
         <v>28</v>
       </c>
       <c r="E15" s="14">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>58</v>
@@ -1350,7 +1350,7 @@
         <v>35</v>
       </c>
       <c r="E18" s="14">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>61</v>
@@ -1413,7 +1413,7 @@
         <v>37</v>
       </c>
       <c r="E21" s="14">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>64</v>
@@ -1476,7 +1476,7 @@
         <v>41</v>
       </c>
       <c r="E24" s="14">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>67</v>
@@ -1518,7 +1518,7 @@
         <v>45</v>
       </c>
       <c r="E26" s="15">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>69</v>

--- a/ebd/static/lista de revistas.xlsx
+++ b/ebd/static/lista de revistas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PDV-01\Desktop\Nova pasta (5)\ebdpesqueira\ebd\static\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D7E00A7-645B-41BC-BB60-B26F5588C9FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8423EE6D-8FC6-4940-A652-AD4606FFD043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{2B98A784-99CC-4906-9103-6760237A2AE9}"/>
   </bookViews>
@@ -256,7 +256,7 @@
     <t>/static/imagem29.png</t>
   </si>
   <si>
-    <t>Devocinal A Santissima Trindade</t>
+    <t>Devocinal Homens dos quais o Mundo não era digno</t>
   </si>
 </sst>
 </file>
@@ -972,7 +972,7 @@
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="48.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.85546875" style="5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="65.7109375" bestFit="1" customWidth="1"/>
